--- a/icm-engine/tests/fixtures/_stmt_iso/statement_P2_all.xlsx
+++ b/icm-engine/tests/fixtures/_stmt_iso/statement_P2_all.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Statement" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Statement" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,16 +426,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Payee</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bob (P2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -450,25 +519,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>rule_id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>base_amount</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>commission</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>adjustment</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -481,27 +560,29 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>5000.00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>250.00</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Flat rate 0.05 on 5000</t>
         </is>
@@ -515,14 +596,16 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>250.00</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
